--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flore\Downloads\CheckLists\CheckLists\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\galal\Desktop\vvss\ProiectVVSS\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4764134-D221-4EDD-AD6B-69AB3B61882B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E176108A-47E1-4B2C-9671-9E5A6CFFB90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="650" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="101">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -315,6 +315,54 @@
   </si>
   <si>
     <t>Effort to perform tool-based code analysis (hours): 20 min</t>
+  </si>
+  <si>
+    <t>Gal Alexandru</t>
+  </si>
+  <si>
+    <t>04.03.2025</t>
+  </si>
+  <si>
+    <t>R01</t>
+  </si>
+  <si>
+    <t>Creare Comanda</t>
+  </si>
+  <si>
+    <t>Nu este specificat dacă o comandă poate fi modificată, anulată sau ce se întâmplă daca stocul este insuficient.</t>
+  </si>
+  <si>
+    <t>R02</t>
+  </si>
+  <si>
+    <t>R04</t>
+  </si>
+  <si>
+    <t>R05</t>
+  </si>
+  <si>
+    <t>R06</t>
+  </si>
+  <si>
+    <t>R07</t>
+  </si>
+  <si>
+    <t>Nu este specificat un sistem de autentificare sau roluri separate pentru chelner/admin</t>
+  </si>
+  <si>
+    <t>Nu se specifică dacă aplicația ar trebui să înceapă cu date predefinite sau cu date goale</t>
+  </si>
+  <si>
+    <t>Conținut Comandă</t>
+  </si>
+  <si>
+    <t>Nu se specifică cazuri de eroare</t>
+  </si>
+  <si>
+    <t>Nu este precizat cine este user-ul, câți useri pot fi simultani și cerințe de performanță</t>
+  </si>
+  <si>
+    <t>Nu este precizată versiunea de Java/JavaFx și sistemul de operare pe care trebuie rulat</t>
   </si>
 </sst>
 </file>
@@ -567,14 +615,23 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -594,20 +651,11 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -917,36 +965,36 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.26953125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="6"/>
     <col min="9" max="9" width="21" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.453125" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.90625" style="6"/>
+    <col min="10" max="10" width="14.42578125" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -966,10 +1014,10 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="28"/>
+      <c r="E4" s="31"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -980,10 +1028,10 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="33"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -995,15 +1043,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+      <c r="D6" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="D7" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="30"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -1019,58 +1071,86 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" ht="45">
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="C10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="30">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="E11" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="45">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="C13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="E14" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="30">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="D15" s="1"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="3">
@@ -1189,35 +1269,35 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.26953125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="22.08984375" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="6"/>
+    <col min="9" max="9" width="22.140625" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1237,10 +1317,10 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="31"/>
+      <c r="E4" s="34"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1251,10 +1331,10 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="33"/>
+      <c r="E5" s="36"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1266,19 +1346,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="25"/>
+      <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="30"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -1294,7 +1374,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" ht="30">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -1308,7 +1388,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="30">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -1353,7 +1433,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="29">
+    <row r="14" spans="1:10" ht="30">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1368,7 +1448,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="30">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1383,7 +1463,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="30">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1529,36 +1609,36 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="26.7265625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="6"/>
+    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1578,10 +1658,10 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="34"/>
+      <c r="E4" s="29"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1592,10 +1672,10 @@
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="36"/>
+      <c r="E5" s="38"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1607,15 +1687,15 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -1846,37 +1926,37 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="23.90625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.6328125" style="6" customWidth="1"/>
-    <col min="7" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="26.7265625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="5" max="5" width="23.85546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" style="6" customWidth="1"/>
+    <col min="7" max="8" width="8.85546875" style="6"/>
+    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1896,8 +1976,8 @@
       <c r="C4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1908,10 +1988,10 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="25"/>
+      <c r="E5" s="30"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1923,10 +2003,10 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="25"/>
+      <c r="E6" s="30"/>
       <c r="F6" s="20"/>
     </row>
     <row r="9" spans="1:10">
@@ -1946,7 +2026,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="58">
+    <row r="10" spans="1:10" ht="60">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -1993,7 +2073,7 @@
       </c>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="43.5">
+    <row r="13" spans="1:10" ht="45">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2011,7 +2091,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="29">
+    <row r="14" spans="1:10" ht="30">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2027,7 +2107,7 @@
       </c>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="43.5">
+    <row r="15" spans="1:10" ht="45">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2045,7 +2125,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="29">
+    <row r="16" spans="1:10" ht="45">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2063,7 +2143,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="58">
+    <row r="17" spans="2:6" ht="60">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2212,11 +2292,11 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="37" t="s">
+      <c r="C32" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
       <c r="F32" s="18"/>
     </row>
     <row r="35" spans="6:6">

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29825"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\galal\Desktop\vvss\ProiectVVSS\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E176108A-47E1-4B2C-9671-9E5A6CFFB90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B42D3A41-BD66-41F6-A03C-8B7EAA8BB498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="650" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -18,8 +18,11 @@
     <sheet name="Coding Phase Defects" sheetId="5" r:id="rId3"/>
     <sheet name="Tool-basedCodeAnalysis" sheetId="8" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,18 +39,54 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="126">
+  <si>
+    <t>do not print this form</t>
+  </si>
+  <si>
+    <t>Echipa</t>
+  </si>
+  <si>
+    <t>Review Form. Requirements Defects</t>
+  </si>
+  <si>
+    <t>Numele si prenumele</t>
+  </si>
+  <si>
+    <t>Grupa</t>
+  </si>
+  <si>
+    <t>Student 1:</t>
+  </si>
   <si>
     <t>Document  Title:</t>
   </si>
   <si>
+    <t>Requirements Document</t>
+  </si>
+  <si>
+    <t>Student 2:</t>
+  </si>
+  <si>
+    <t>Author Name:</t>
+  </si>
+  <si>
+    <t>Firicescu George</t>
+  </si>
+  <si>
+    <t>Student 3:</t>
+  </si>
+  <si>
+    <t>Reviewer Name:</t>
+  </si>
+  <si>
+    <t>Gal Alexandru</t>
+  </si>
+  <si>
     <t xml:space="preserve">Review date: </t>
   </si>
   <si>
-    <t>Reviewer Name:</t>
-  </si>
-  <si>
-    <t>do not print this form</t>
+    <t>04.03.2025</t>
   </si>
   <si>
     <t>Crt. No.</t>
@@ -62,166 +101,256 @@
     <t>Comments/ improvements</t>
   </si>
   <si>
+    <t>R01</t>
+  </si>
+  <si>
+    <t>Creare Comanda</t>
+  </si>
+  <si>
+    <t>Nu este specificat dacă o comandă poate fi modificată, anulată sau ce se întâmplă daca stocul este insuficient.</t>
+  </si>
+  <si>
+    <t>R02</t>
+  </si>
+  <si>
+    <t>Nu este specificat un sistem de autentificare sau roluri separate pentru chelner/admin</t>
+  </si>
+  <si>
+    <t>R04</t>
+  </si>
+  <si>
+    <t>Nu se specifică dacă aplicația ar trebui să înceapă cu date predefinite sau cu date goale</t>
+  </si>
+  <si>
+    <t>R05</t>
+  </si>
+  <si>
+    <t>Conținut Comandă</t>
+  </si>
+  <si>
+    <t>Nu se specifică cazuri de eroare</t>
+  </si>
+  <si>
+    <t>R06</t>
+  </si>
+  <si>
+    <t>Nu este precizat cine este user-ul, câți useri pot fi simultani și cerințe de performanță</t>
+  </si>
+  <si>
+    <t>R07</t>
+  </si>
+  <si>
+    <t>Nu este precizată versiunea de Java/JavaFx și sistemul de operare pe care trebuie rulat</t>
+  </si>
+  <si>
     <t>Effort to review document (hours):</t>
   </si>
   <si>
-    <t>Author Name:</t>
+    <t>Review Form. Architectural Design Defects</t>
+  </si>
+  <si>
+    <t>Architectural Design Document</t>
   </si>
   <si>
     <t xml:space="preserve">Author Name: </t>
   </si>
   <si>
+    <t>Georgescu Anca</t>
+  </si>
+  <si>
+    <t>Florea Ariana Ioana</t>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>Stoc</t>
+  </si>
+  <si>
+    <t>Nu detine un obiect de tip ingredient desi trebuie</t>
+  </si>
+  <si>
+    <t>IngrenientReteta</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>Validator</t>
+  </si>
+  <si>
+    <t>Nu se folosesc validatoarele</t>
+  </si>
+  <si>
+    <t>Cantintati</t>
+  </si>
+  <si>
+    <t>Nu exista tipuri de cantitati</t>
+  </si>
+  <si>
+    <t>A02</t>
+  </si>
+  <si>
+    <t>DrinkShopController</t>
+  </si>
+  <si>
+    <t>Creeaza produse noi, nu e ok, trebe sa lucreze cu servicii</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>CategorieBautura</t>
+  </si>
+  <si>
+    <t>este de tip enum deci nu se pot adauga/sterge</t>
+  </si>
+  <si>
+    <t>TipBautura</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>nu exista asociere produs reteta</t>
+  </si>
+  <si>
+    <t>FileOrderRepository</t>
+  </si>
+  <si>
+    <t>Are relatie directa cu interfata repository</t>
+  </si>
+  <si>
+    <t>25 min</t>
+  </si>
+  <si>
+    <t>Review Form. Coding Defects</t>
+  </si>
+  <si>
+    <t>Coding Document</t>
+  </si>
+  <si>
     <t>Popescu Ionel</t>
   </si>
   <si>
-    <t>Georgescu Anca</t>
-  </si>
-  <si>
-    <t>Firicescu George</t>
-  </si>
-  <si>
-    <t>Requirements Document</t>
-  </si>
-  <si>
-    <t>Architectural Design Document</t>
-  </si>
-  <si>
-    <t>Coding Document</t>
-  </si>
-  <si>
-    <t>Review Form. Coding Defects</t>
-  </si>
-  <si>
-    <t>Review Form. Architectural Design Defects</t>
-  </si>
-  <si>
-    <t>Review Form. Requirements Defects</t>
-  </si>
-  <si>
-    <t>Student 1:</t>
-  </si>
-  <si>
-    <t>Student 2:</t>
-  </si>
-  <si>
-    <t>Student 3:</t>
-  </si>
-  <si>
-    <t>Echipa</t>
-  </si>
-  <si>
-    <t>Grupa</t>
+    <t>Gabor Dacian-Carlos-Ionut</t>
+  </si>
+  <si>
+    <t>06.03.2026</t>
+  </si>
+  <si>
+    <t>C06</t>
+  </si>
+  <si>
+    <t>OrderService/21</t>
+  </si>
+  <si>
+    <t>O comanda poate fi creata fara iteme / Trebuie verificat in OrderService daca order-ul este gol</t>
+  </si>
+  <si>
+    <t>Product/11</t>
+  </si>
+  <si>
+    <t>Nu exista validarii in constructor / Adaugam validari</t>
+  </si>
+  <si>
+    <t>Repositories</t>
+  </si>
+  <si>
+    <t>Nu exista validari in cazul in care in split lipsesc fragmente</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>Nu exista validari in cazul in care repo-urile sunt empty</t>
+  </si>
+  <si>
+    <t>DrinkShopController/171</t>
+  </si>
+  <si>
+    <t>Nu se verifica daca text box-urile sunt goale, asadar pot aparea erori la conversia in double / Se adauga verificari</t>
+  </si>
+  <si>
+    <t>C08</t>
+  </si>
+  <si>
+    <t>IngredientReteta/8</t>
+  </si>
+  <si>
+    <t>Nu se verifica daca denumirea este goala, prin urmare pot fi adaugate ingrediente fara nume ceea ce nu este ideal / Se adauga verificari</t>
+  </si>
+  <si>
+    <t>DrinkShopController/97</t>
+  </si>
+  <si>
+    <t>Se poate adauga o reteta fara ingrediente / Adaugam verificare</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>DrinkShopController/123</t>
+  </si>
+  <si>
+    <t>Nu se poate adauga un nou produs / Corectare conditie din if</t>
+  </si>
+  <si>
+    <t>C07</t>
+  </si>
+  <si>
+    <t>DailyReportService/18</t>
+  </si>
+  <si>
+    <t>Raportul nu se calculeaza corect in cazul in care sunt adaugate comenzi goale / Adaugam verificari</t>
+  </si>
+  <si>
+    <t>50 min</t>
+  </si>
+  <si>
+    <t>Tool-based Code Analysis</t>
   </si>
   <si>
     <t>Tool used:</t>
   </si>
   <si>
+    <t>Florea Ariana</t>
+  </si>
+  <si>
+    <t>04.03.2026</t>
+  </si>
+  <si>
+    <t>File, Line</t>
+  </si>
+  <si>
+    <t>Issue</t>
+  </si>
+  <si>
     <t>Before</t>
   </si>
   <si>
-    <t>Issue</t>
-  </si>
-  <si>
-    <t>File, Line</t>
-  </si>
-  <si>
     <t>After/Argument</t>
   </si>
   <si>
-    <t>Numele si prenumele</t>
-  </si>
-  <si>
-    <t>Tool-based Code Analysis</t>
-  </si>
-  <si>
-    <t>A02</t>
-  </si>
-  <si>
-    <t>A03</t>
-  </si>
-  <si>
-    <t>A05</t>
-  </si>
-  <si>
-    <t>A10</t>
-  </si>
-  <si>
-    <t>Stoc</t>
-  </si>
-  <si>
-    <t>IngrenientReteta</t>
-  </si>
-  <si>
-    <t>Validator</t>
-  </si>
-  <si>
-    <t>Nu se folosesc validatoarele</t>
-  </si>
-  <si>
-    <t>Cantintati</t>
-  </si>
-  <si>
-    <t>Nu exista tipuri de cantitati</t>
-  </si>
-  <si>
-    <t>DrinkShopController</t>
-  </si>
-  <si>
-    <t>Creeaza produse noi, nu e ok, trebe sa lucreze cu servicii</t>
-  </si>
-  <si>
-    <t>CategorieBautura</t>
-  </si>
-  <si>
-    <t>este de tip enum deci nu se pot adauga/sterge</t>
-  </si>
-  <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>nu exista asociere produs reteta</t>
-  </si>
-  <si>
-    <t>FileOrderRepository</t>
-  </si>
-  <si>
-    <t>Are relatie directa cu interfata repository</t>
-  </si>
-  <si>
-    <t>Florea Ariana Ioana</t>
-  </si>
-  <si>
-    <t>03.03.2026</t>
-  </si>
-  <si>
-    <t>Nu detine un obiect de tip ingredient desi trebuie</t>
-  </si>
-  <si>
-    <t>25 min</t>
-  </si>
-  <si>
-    <t>Florea Ariana</t>
-  </si>
-  <si>
-    <t>04.03.2026</t>
-  </si>
-  <si>
     <t>ProductService, 49</t>
   </si>
   <si>
+    <t>toList instead of collectors when unmodifiable list needed</t>
+  </si>
+  <si>
+    <t>collect(Collectors.toList())</t>
+  </si>
+  <si>
+    <t>toList()</t>
+  </si>
+  <si>
+    <t>ProductServuce, 30</t>
+  </si>
+  <si>
     <t>Block of comment(code)</t>
-  </si>
-  <si>
-    <t>collect(Collectors.toList())</t>
-  </si>
-  <si>
-    <t>toList()</t>
-  </si>
-  <si>
-    <t>ProductServuce, 30</t>
-  </si>
-  <si>
-    <t>toList instead of collectors when unmodifiable list needed</t>
   </si>
   <si>
     <t>CsvExporter, 11</t>
@@ -266,6 +395,9 @@
     <t>(List)</t>
   </si>
   <si>
+    <t>Order Validator, 31</t>
+  </si>
+  <si>
     <t>Strings should not be concatenated using '+' in a loop</t>
   </si>
   <si>
@@ -273,6 +405,9 @@
   </si>
   <si>
     <t>StringBuilder</t>
+  </si>
+  <si>
+    <t>RetetaValidator, 22</t>
   </si>
   <si>
     <t>Null pointers should not be dereferenced</t>
@@ -296,12 +431,6 @@
     <t>daca ii null, nu se face stream pe el</t>
   </si>
   <si>
-    <t>RetetaValidator, 22</t>
-  </si>
-  <si>
-    <t>Order Validator, 31</t>
-  </si>
-  <si>
     <t>Multiple variables should not be declared on the same line</t>
   </si>
   <si>
@@ -311,92 +440,20 @@
     <t>nu vreau sa schimb pentru ca nu este nimic gresit in acest caz</t>
   </si>
   <si>
-    <t>TipBautura</t>
-  </si>
-  <si>
     <t>Effort to perform tool-based code analysis (hours): 20 min</t>
-  </si>
-  <si>
-    <t>Gal Alexandru</t>
-  </si>
-  <si>
-    <t>04.03.2025</t>
-  </si>
-  <si>
-    <t>R01</t>
-  </si>
-  <si>
-    <t>Creare Comanda</t>
-  </si>
-  <si>
-    <t>Nu este specificat dacă o comandă poate fi modificată, anulată sau ce se întâmplă daca stocul este insuficient.</t>
-  </si>
-  <si>
-    <t>R02</t>
-  </si>
-  <si>
-    <t>R04</t>
-  </si>
-  <si>
-    <t>R05</t>
-  </si>
-  <si>
-    <t>R06</t>
-  </si>
-  <si>
-    <t>R07</t>
-  </si>
-  <si>
-    <t>Nu este specificat un sistem de autentificare sau roluri separate pentru chelner/admin</t>
-  </si>
-  <si>
-    <t>Nu se specifică dacă aplicația ar trebui să înceapă cu date predefinite sau cu date goale</t>
-  </si>
-  <si>
-    <t>Conținut Comandă</t>
-  </si>
-  <si>
-    <t>Nu se specifică cazuri de eroare</t>
-  </si>
-  <si>
-    <t>Nu este precizat cine este user-ul, câți useri pot fi simultani și cerințe de performanță</t>
-  </si>
-  <si>
-    <t>Nu este precizată versiunea de Java/JavaFx și sistemul de operare pe care trebuie rulat</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -575,87 +632,84 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -967,202 +1021,286 @@
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="6"/>
-    <col min="9" max="9" width="21" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="5"/>
+    <col min="2" max="2" width="12.28515625" style="5" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="5" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="5"/>
+    <col min="9" max="9" width="21" style="5" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="16"/>
+      <c r="B2" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="B2" s="28" t="s">
+      <c r="J2" s="20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="27"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="16"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="22"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="22"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="16"/>
+      <c r="B9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="H3" s="17" t="s">
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" spans="1:10" ht="45">
+      <c r="A10" s="16"/>
+      <c r="B10" s="20">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="C4" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="31"/>
-      <c r="H4" s="17" t="s">
+      <c r="D10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="C5" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="33"/>
-      <c r="H5" s="17" t="s">
+      <c r="E10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="30"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="C7" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" s="30"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="45">
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>89</v>
-      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
     </row>
     <row r="11" spans="1:10" ht="30">
-      <c r="B11" s="3">
+      <c r="A11" s="16"/>
+      <c r="B11" s="20">
         <f>B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="2" t="s">
-        <v>95</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
     </row>
     <row r="12" spans="1:10" ht="45">
-      <c r="B12" s="3">
+      <c r="A12" s="16"/>
+      <c r="B12" s="20">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="2" t="s">
-        <v>96</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="B13" s="3">
+      <c r="A13" s="16"/>
+      <c r="B13" s="20">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>98</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
     </row>
     <row r="14" spans="1:10" ht="30">
-      <c r="B14" s="3">
+      <c r="A14" s="16"/>
+      <c r="B14" s="20">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="2" t="s">
-        <v>99</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:10" ht="30">
-      <c r="B15" s="3">
+      <c r="A15" s="16"/>
+      <c r="B15" s="20">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="2" t="s">
-        <v>100</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="B16" s="3">
+      <c r="A16" s="16"/>
+      <c r="B16" s="20">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="2"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
     </row>
     <row r="17" spans="2:5">
-      <c r="B17" s="3">
+      <c r="B17" s="20">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1171,82 +1309,83 @@
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="3">
+      <c r="B18" s="20">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="15"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="21"/>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="3">
+      <c r="B19" s="20">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="15"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="21"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="3">
+      <c r="B20" s="20">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="15"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="21"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="3">
+      <c r="B21" s="20">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="15"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="21"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="3">
+      <c r="B22" s="20">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="15"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="21"/>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="3">
+      <c r="B23" s="20">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="15"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="21"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="3">
+      <c r="B24" s="20">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="15"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="21"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="3">
+      <c r="B25" s="20">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="15"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="21"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="C27" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="12"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="11"/>
       <c r="E27" s="1"/>
     </row>
   </sheetData>
@@ -1271,245 +1410,329 @@
   <dimension ref="A1:J28"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="6"/>
-    <col min="9" max="9" width="22.140625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="5"/>
+    <col min="2" max="2" width="12.28515625" style="5" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="5" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="5"/>
+    <col min="9" max="9" width="22.140625" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="16"/>
+      <c r="B2" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="B2" s="28" t="s">
+      <c r="J2" s="20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="28"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="30"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="16"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="22"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="22"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="16"/>
+      <c r="B9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="C4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="34"/>
-      <c r="H4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="C5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="36"/>
-      <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="30"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="C7" s="9" t="s">
+      <c r="E9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" spans="1:10" ht="30">
+      <c r="A10" s="16"/>
+      <c r="B10" s="20">
         <v>1</v>
       </c>
-      <c r="D7" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="30"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="30">
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>52</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
     </row>
     <row r="11" spans="1:10" ht="30">
-      <c r="B11" s="3">
+      <c r="A11" s="16"/>
+      <c r="B11" s="20">
         <f>B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>52</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="B12" s="3">
+      <c r="A12" s="16"/>
+      <c r="B12" s="20">
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>39</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="B13" s="3">
+      <c r="A13" s="16"/>
+      <c r="B13" s="20">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+    </row>
+    <row r="14" spans="1:10" ht="30">
+      <c r="A14" s="16"/>
+      <c r="B14" s="20">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+    </row>
+    <row r="15" spans="1:10" ht="30">
+      <c r="A15" s="16"/>
+      <c r="B15" s="20">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+    </row>
+    <row r="16" spans="1:10" ht="30">
+      <c r="A16" s="16"/>
+      <c r="B16" s="20">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="20">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="30">
-      <c r="B14" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="30">
-      <c r="B15" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="30">
-      <c r="B16" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="3">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="3">
+      <c r="B18" s="20">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="3">
+      <c r="B19" s="20">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1518,7 +1741,7 @@
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="3">
+      <c r="B20" s="20">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -1527,7 +1750,7 @@
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="3">
+      <c r="B21" s="20">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1536,7 +1759,7 @@
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="3">
+      <c r="B22" s="20">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -1545,7 +1768,7 @@
       <c r="E22" s="2"/>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="3">
+      <c r="B23" s="20">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -1554,7 +1777,7 @@
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="3">
+      <c r="B24" s="20">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1563,7 +1786,7 @@
       <c r="E24" s="2"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="3">
+      <c r="B25" s="20">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1572,7 +1795,7 @@
       <c r="E25" s="2"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="3">
+      <c r="B26" s="20">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -1581,12 +1804,13 @@
       <c r="E26" s="2"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="C28" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="12"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="11"/>
       <c r="E28" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1611,188 +1835,330 @@
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="6"/>
-    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="5"/>
+    <col min="2" max="2" width="12.28515625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18" style="5" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="5" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="5"/>
+    <col min="9" max="9" width="26.7109375" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="16"/>
+      <c r="B2" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="B2" s="28" t="s">
+      <c r="J2" s="20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="31"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="33"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="16"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="22"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="22"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="16"/>
+      <c r="B9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="C4" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="29"/>
-      <c r="H4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="C5" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="38"/>
-      <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="C7" s="9" t="s">
+      <c r="D9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" spans="1:10" ht="45.75">
+      <c r="A10" s="16"/>
+      <c r="B10" s="20">
         <v>1</v>
       </c>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="B11" s="3">
+      <c r="C10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+    </row>
+    <row r="11" spans="1:10" ht="30.75">
+      <c r="A11" s="16"/>
+      <c r="B11" s="20">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="B12" s="3">
+      <c r="C11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+    </row>
+    <row r="12" spans="1:10" ht="30.75">
+      <c r="A12" s="16"/>
+      <c r="B12" s="20">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="B13" s="3">
+      <c r="C12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13" spans="1:10" ht="30.75">
+      <c r="A13" s="16"/>
+      <c r="B13" s="20">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="3">
+      <c r="C13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+    </row>
+    <row r="14" spans="1:10" ht="45.75">
+      <c r="A14" s="16"/>
+      <c r="B14" s="20">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="3">
+      <c r="C14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+    </row>
+    <row r="15" spans="1:10" ht="45.75">
+      <c r="A15" s="16"/>
+      <c r="B15" s="20">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="3">
+      <c r="C15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+    </row>
+    <row r="16" spans="1:10" ht="30.75">
+      <c r="A16" s="16"/>
+      <c r="B16" s="20">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="3">
+      <c r="C16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+    </row>
+    <row r="17" spans="2:5" ht="30.75">
+      <c r="B17" s="20">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="2:5">
-      <c r="B18" s="3">
+      <c r="C17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="45.75">
+      <c r="B18" s="20">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="C18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="3">
+      <c r="B19" s="20">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1801,7 +2167,7 @@
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="3">
+      <c r="B20" s="20">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -1810,7 +2176,7 @@
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="3">
+      <c r="B21" s="20">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1819,7 +2185,7 @@
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="3">
+      <c r="B22" s="20">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -1828,7 +2194,7 @@
       <c r="E22" s="2"/>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="3">
+      <c r="B23" s="20">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -1837,7 +2203,7 @@
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="3">
+      <c r="B24" s="20">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1846,7 +2212,7 @@
       <c r="E24" s="2"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="3">
+      <c r="B25" s="20">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1855,7 +2221,7 @@
       <c r="E25" s="2"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="3">
+      <c r="B26" s="20">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -1864,7 +2230,7 @@
       <c r="E26" s="2"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="3">
+      <c r="B27" s="20">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -1873,7 +2239,7 @@
       <c r="E27" s="1"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="3">
+      <c r="B28" s="20">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -1882,7 +2248,7 @@
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="3">
+      <c r="B29" s="20">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -1891,7 +2257,7 @@
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="3">
+      <c r="B30" s="20">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -1900,11 +2266,14 @@
       <c r="E30" s="2"/>
     </row>
     <row r="32" spans="2:5">
-      <c r="C32" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="12"/>
-      <c r="E32" s="1"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="11"/>
+      <c r="E32" s="1" t="s">
+        <v>89</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1928,241 +2297,309 @@
   <dimension ref="A1:J35"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" style="6" customWidth="1"/>
-    <col min="7" max="8" width="8.85546875" style="6"/>
-    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="5"/>
+    <col min="2" max="2" width="12.28515625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18" style="5" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" style="5" customWidth="1"/>
+    <col min="7" max="8" width="8.85546875" style="5"/>
+    <col min="9" max="9" width="26.7109375" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="16"/>
+      <c r="B2" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="B2" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>24</v>
+      <c r="J2" s="20" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="C4" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="H4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="C5" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="30"/>
-      <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="22"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
+      <c r="A6" s="16"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="22"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="16"/>
+      <c r="B9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" spans="1:10" ht="60">
+      <c r="A10" s="16"/>
+      <c r="B10" s="20">
         <v>1</v>
       </c>
-      <c r="D6" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="20"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="60">
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>58</v>
+        <v>99</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>100</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="B11" s="3">
+      <c r="A11" s="16"/>
+      <c r="B11" s="20">
         <f>B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="B12" s="3">
+      <c r="A12" s="16"/>
+      <c r="B12" s="20">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>64</v>
+        <v>105</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>106</v>
       </c>
       <c r="F12" s="2"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:10" ht="45">
-      <c r="B13" s="3">
+      <c r="A13" s="16"/>
+      <c r="B13" s="20">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>68</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
     </row>
     <row r="14" spans="1:10" ht="30">
-      <c r="B14" s="3">
+      <c r="A14" s="16"/>
+      <c r="B14" s="20">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="F14" s="2"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:10" ht="45">
-      <c r="B15" s="3">
+      <c r="A15" s="16"/>
+      <c r="B15" s="20">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>74</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:10" ht="45">
-      <c r="B16" s="3">
+      <c r="A16" s="16"/>
+      <c r="B16" s="20">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>76</v>
+        <v>119</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>77</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
     </row>
     <row r="17" spans="2:6" ht="60">
-      <c r="B17" s="3">
+      <c r="B17" s="20">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>81</v>
+        <v>122</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>123</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="3">
+      <c r="B18" s="20">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -2172,7 +2609,7 @@
       <c r="F18" s="2"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" s="3">
+      <c r="B19" s="20">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2182,7 +2619,7 @@
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="2:6">
-      <c r="B20" s="3">
+      <c r="B20" s="20">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -2192,7 +2629,7 @@
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="2:6">
-      <c r="B21" s="3">
+      <c r="B21" s="20">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -2202,7 +2639,7 @@
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="2:6">
-      <c r="B22" s="3">
+      <c r="B22" s="20">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -2212,7 +2649,7 @@
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="2:6">
-      <c r="B23" s="3">
+      <c r="B23" s="20">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -2222,7 +2659,7 @@
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="2:6">
-      <c r="B24" s="3">
+      <c r="B24" s="20">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -2232,7 +2669,7 @@
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="3">
+      <c r="B25" s="20">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -2242,7 +2679,7 @@
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="2:6">
-      <c r="B26" s="3">
+      <c r="B26" s="20">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -2252,7 +2689,7 @@
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="3">
+      <c r="B27" s="20">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -2262,7 +2699,7 @@
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="B28" s="3">
+      <c r="B28" s="20">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -2272,7 +2709,7 @@
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="B29" s="3">
+      <c r="B29" s="20">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -2282,7 +2719,7 @@
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="3">
+      <c r="B30" s="20">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -2292,15 +2729,16 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="18"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="15"/>
     </row>
     <row r="35" spans="6:6">
-      <c r="F35" s="21"/>
+      <c r="F35" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="6">
